--- a/Dimensions.xlsx
+++ b/Dimensions.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\08-MyCOOCharter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D32C1E-A91C-4AB1-BB65-C471F120260E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB85AA3-148F-4E19-80CF-5741B58282DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CustomerArchetype" sheetId="1" r:id="rId1"/>
-    <sheet name="CustomerArchetype-Instantiation" sheetId="4" r:id="rId2"/>
-    <sheet name="EnhancedArchitypeStructure" sheetId="2" r:id="rId3"/>
+    <sheet name="EnhancedArchitypeStructure" sheetId="2" r:id="rId2"/>
+    <sheet name="WhatWhyWhynot" sheetId="5" r:id="rId3"/>
+    <sheet name="CustomerArchetype-Instantiation" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="470">
   <si>
     <t>Archetype Bucket</t>
   </si>
@@ -110,42 +111,18 @@
     <t>Enhancement Lever</t>
   </si>
   <si>
-    <t>AI/GenAI</t>
-  </si>
-  <si>
     <t>Attitude towards AI</t>
   </si>
   <si>
-    <t>Are they an AI enthusiast, pragmatist, skeptic, or laggard?</t>
-  </si>
-  <si>
-    <t>Primary AI Need</t>
-  </si>
-  <si>
-    <t>What specific problem could AI/GenAI solve for them right now? (e.g., efficiency, insight, innovation, risk mitigation).</t>
-  </si>
-  <si>
     <t>Contextual Modifiers</t>
   </si>
   <si>
     <t>Relationship Status</t>
   </si>
   <si>
-    <t>Preferred Partner, Primary Vendor, Secondary Vendor, 1 of Many and Not Present</t>
-  </si>
-  <si>
     <t>Capability Perception</t>
   </si>
   <si>
-    <t>Execution, Innovation, Skill, Pricing</t>
-  </si>
-  <si>
-    <t>Geographic Lens</t>
-  </si>
-  <si>
-    <t>what regional trends (e.g., EU's focus on data privacy via the AI Act, North America's drive for commercialization) color their perspective?</t>
-  </si>
-  <si>
     <t>The Doer</t>
   </si>
   <si>
@@ -312,13 +289,1232 @@
   </si>
   <si>
     <t>The Pragmatic</t>
+  </si>
+  <si>
+    <t>Archetype Group</t>
+  </si>
+  <si>
+    <t>Top Key Expectations (The 'What')</t>
+  </si>
+  <si>
+    <t>Top Drivers / Latent Needs (The 'Why')</t>
+  </si>
+  <si>
+    <t>Top AI Adoption Blockers (The 'Why Not')</t>
+  </si>
+  <si>
+    <t>Decision-Makers</t>
+  </si>
+  <si>
+    <t>Hands-On Users</t>
+  </si>
+  <si>
+    <t>Influencers &amp; Champions</t>
+  </si>
+  <si>
+    <t>Gatekeepers &amp; Skeptics</t>
+  </si>
+  <si>
+    <t>Partners &amp; Ecosystem</t>
+  </si>
+  <si>
+    <t>The Visionary Executive</t>
+  </si>
+  <si>
+    <t>The Pragmatic Director</t>
+  </si>
+  <si>
+    <t>The Cost-Conscious Buyer</t>
+  </si>
+  <si>
+    <t>The Daily Doer</t>
+  </si>
+  <si>
+    <t>The Overwhelmed Onboarder</t>
+  </si>
+  <si>
+    <t>The Technical Evaluator</t>
+  </si>
+  <si>
+    <t>The Innovator</t>
+  </si>
+  <si>
+    <t>The Data-Driven Analyst</t>
+  </si>
+  <si>
+    <t>The Security Sentinel</t>
+  </si>
+  <si>
+    <r>
+      <t>Key Expectations (The 'What'):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1B1C1D"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> These are the contractual requirements and the features they ask for. This is their </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF1B1C1D"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>stated</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1B1C1D"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> position.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1B1C1D"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Drivers / Latent Needs (The 'Why'): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1B1C1D"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>These are the underlying personal, political, or strategic motivations. This is what drives their real decisions.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1B1C1D"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+AI Adoption Blockers (The 'Why Not'): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1B1C1D"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>These are the specific fears and risks that we must proactively address to even begin a conversation about AI/GenAI solutions.</t>
+    </r>
+  </si>
+  <si>
+    <t>Strategic Cost Savings</t>
+  </si>
+  <si>
+    <t>Scalability &amp; Performance</t>
+  </si>
+  <si>
+    <t>Access to Skilled Experts</t>
+  </si>
+  <si>
+    <t>Gaining Competitive Advantage</t>
+  </si>
+  <si>
+    <t>Enabling Business Transformation</t>
+  </si>
+  <si>
+    <t>Demonstrating Innovation</t>
+  </si>
+  <si>
+    <t>Future-Proofing the Tech Stack</t>
+  </si>
+  <si>
+    <t>Personal Legacy &amp; Industry Recognition</t>
+  </si>
+  <si>
+    <t>Unclear ROI / Business Case</t>
+  </si>
+  <si>
+    <t>IP &amp; Data Ownership Concerns</t>
+  </si>
+  <si>
+    <t>Regulatory &amp; Compliance Uncertainty</t>
+  </si>
+  <si>
+    <t>Potential for Brand-Damaging Bias/Ethics</t>
+  </si>
+  <si>
+    <t>High Implementation Cost</t>
+  </si>
+  <si>
+    <t>Productivity Gains</t>
+  </si>
+  <si>
+    <t>Reliability / High Availability</t>
+  </si>
+  <si>
+    <t>Seamless Integration</t>
+  </si>
+  <si>
+    <t>Excellent Technical Support</t>
+  </si>
+  <si>
+    <t>IT-Business Alignment</t>
+  </si>
+  <si>
+    <t>Reducing Team Workload &amp; Stress</t>
+  </si>
+  <si>
+    <t>Mitigating Operational Risk</t>
+  </si>
+  <si>
+    <t>Personal Career Advancement</t>
+  </si>
+  <si>
+    <t>Vendor Consolidation</t>
+  </si>
+  <si>
+    <t>High Implementation Cost &amp; Effort</t>
+  </si>
+  <si>
+    <t>Lack of In-House Skills</t>
+  </si>
+  <si>
+    <t>Integration Complexity</t>
+  </si>
+  <si>
+    <t>Fear of Business Disruption</t>
+  </si>
+  <si>
+    <t>Lower TCO / Cost Savings</t>
+  </si>
+  <si>
+    <t>Clear, Predictable Pricing</t>
+  </si>
+  <si>
+    <t>Favorable Contract Terms</t>
+  </si>
+  <si>
+    <t>Basic Reliability &amp; Security</t>
+  </si>
+  <si>
+    <t>Meets Minimum Requirements</t>
+  </si>
+  <si>
+    <t>Reducing Departmental Spend</t>
+  </si>
+  <si>
+    <t>Standardization of Processes</t>
+  </si>
+  <si>
+    <t>Mitigating Financial Risk</t>
+  </si>
+  <si>
+    <t>Demonstrating Fiscal Responsibility</t>
+  </si>
+  <si>
+    <t>Hidden Costs of AI</t>
+  </si>
+  <si>
+    <t>Vague promises of "Productivity"</t>
+  </si>
+  <si>
+    <t>Expensive AI specialist skills needed</t>
+  </si>
+  <si>
+    <t>The Startup Mindset</t>
+  </si>
+  <si>
+    <t>Faster Time to Production</t>
+  </si>
+  <si>
+    <t>Faster Time to Market</t>
+  </si>
+  <si>
+    <t>Actionable Analytics &amp; Insights</t>
+  </si>
+  <si>
+    <t>Lower TCO (Total Cost of Ownership)</t>
+  </si>
+  <si>
+    <t>Low Initial Cost</t>
+  </si>
+  <si>
+    <t>Ease of Use</t>
+  </si>
+  <si>
+    <t>Access to a Community/Support</t>
+  </si>
+  <si>
+    <t>Survival &amp; Market Traction</t>
+  </si>
+  <si>
+    <t>Attracting Talent &amp; Investors</t>
+  </si>
+  <si>
+    <t>Simplifying Complexity (few staff)</t>
+  </si>
+  <si>
+    <t>Unclear ROI</t>
+  </si>
+  <si>
+    <t>Data Privacy (customer trust is key)</t>
+  </si>
+  <si>
+    <t>Fear of vendor lock-in</t>
+  </si>
+  <si>
+    <t>Ease of Use / Intuitive UX</t>
+  </si>
+  <si>
+    <t>Good Technical Support</t>
+  </si>
+  <si>
+    <t>Faster Performance</t>
+  </si>
+  <si>
+    <t>Reducing Personal Workload &amp; Stress</t>
+  </si>
+  <si>
+    <t>Simplifying Complexity</t>
+  </si>
+  <si>
+    <t>Making My Job Easier</t>
+  </si>
+  <si>
+    <t>Avoiding Errors in my Work</t>
+  </si>
+  <si>
+    <t>Keeping up with team demands</t>
+  </si>
+  <si>
+    <t>Fear of Job Displacement</t>
+  </si>
+  <si>
+    <t>Risk of Inaccurate Outputs ("Hallucinations")</t>
+  </si>
+  <si>
+    <t>Lack of Explainability (Don't trust it)</t>
+  </si>
+  <si>
+    <t>Don't want to learn a new complex tool</t>
+  </si>
+  <si>
+    <t>My data being used to train a model</t>
+  </si>
+  <si>
+    <t>Customization &amp; Flexibility</t>
+  </si>
+  <si>
+    <t>Seamless Integration (APIs)</t>
+  </si>
+  <si>
+    <t>Access to Advanced Features</t>
+  </si>
+  <si>
+    <t>Actionable Analytics</t>
+  </si>
+  <si>
+    <t>Simplifying Complexity (of their advanced tasks)</t>
+  </si>
+  <si>
+    <t>Gaining Deeper Insights</t>
+  </si>
+  <si>
+    <t>Personal Career Advancement (as an expert)</t>
+  </si>
+  <si>
+    <t>Pushing the boundaries of what's possible</t>
+  </si>
+  <si>
+    <t>Building unique solutions</t>
+  </si>
+  <si>
+    <t>Lack of control over AI models</t>
+  </si>
+  <si>
+    <t>Risk of Inaccurate Outputs</t>
+  </si>
+  <si>
+    <t>Watered-down features for mainstream users</t>
+  </si>
+  <si>
+    <t>IP &amp; Data Ownership of my creations</t>
+  </si>
+  <si>
+    <t>Excellent Documentation &amp; Training</t>
+  </si>
+  <si>
+    <t>Responsive Technical Support</t>
+  </si>
+  <si>
+    <t>Pre-built templates/workflows</t>
+  </si>
+  <si>
+    <t>Simple, clear navigation</t>
+  </si>
+  <si>
+    <t>Reducing Personal Stress &amp; Anxiety</t>
+  </si>
+  <si>
+    <t>Getting up to speed quickly</t>
+  </si>
+  <si>
+    <t>Not looking incompetent</t>
+  </si>
+  <si>
+    <t>Building confidence in my new role</t>
+  </si>
+  <si>
+    <t>Finding answers without asking for help</t>
+  </si>
+  <si>
+    <t>Adds another layer of complexity to learning</t>
+  </si>
+  <si>
+    <t>Fear of making AI-powered mistakes</t>
+  </si>
+  <si>
+    <t>Lack of Explainability (how did it do that?)</t>
+  </si>
+  <si>
+    <t>Information overload from AI suggestions</t>
+  </si>
+  <si>
+    <t>Fear of Job Displacement (before I've even started)</t>
+  </si>
+  <si>
+    <t>Faster MTTR (Mean Time To Resolution)</t>
+  </si>
+  <si>
+    <t>Actionable Analytics (for root cause)</t>
+  </si>
+  <si>
+    <t>Proactive Alerting</t>
+  </si>
+  <si>
+    <t>Reducing Personal Stress &amp; Workload</t>
+  </si>
+  <si>
+    <t>Moving from reactive to proactive</t>
+  </si>
+  <si>
+    <t>Not getting called at 2 AM</t>
+  </si>
+  <si>
+    <t>Lack of Explainability (Can't trust its diagnosis)</t>
+  </si>
+  <si>
+    <t>Risk of Inaccurate Outputs (False positives)</t>
+  </si>
+  <si>
+    <t>Adds complexity to troubleshooting</t>
+  </si>
+  <si>
+    <t>Fear of deskilling / losing expertise</t>
+  </si>
+  <si>
+    <t>Data Privacy (accessing sensitive logs)</t>
+  </si>
+  <si>
+    <t>Enhanced Security</t>
+  </si>
+  <si>
+    <t>Clear technical documentation</t>
+  </si>
+  <si>
+    <t>Adherence to open standards</t>
+  </si>
+  <si>
+    <t>Mitigating Technical Risk</t>
+  </si>
+  <si>
+    <t>Personal credibility as a tech expert</t>
+  </si>
+  <si>
+    <t>Lack of Explainability</t>
+  </si>
+  <si>
+    <t>Data Privacy &amp; Security Risks</t>
+  </si>
+  <si>
+    <t>Unproven technology at scale</t>
+  </si>
+  <si>
+    <t>Innovative Features</t>
+  </si>
+  <si>
+    <t>Actionable Analytics (to prove value)</t>
+  </si>
+  <si>
+    <t>Access to Skilled Experts &amp; Roadmaps</t>
+  </si>
+  <si>
+    <t>Faster Time to Market (for their projects)</t>
+  </si>
+  <si>
+    <t>Great case studies &amp; references</t>
+  </si>
+  <si>
+    <t>Enabling Business Transformation (of their dept)</t>
+  </si>
+  <si>
+    <t>Gaining visibility in the company</t>
+  </si>
+  <si>
+    <t>Making their team/dept successful</t>
+  </si>
+  <si>
+    <t>Unclear ROI (makes them look bad)</t>
+  </si>
+  <si>
+    <t>High Cost (undermines their business case)</t>
+  </si>
+  <si>
+    <t>Risk of a failed implementation</t>
+  </si>
+  <si>
+    <t>Ethical/Bias issues reflecting on them</t>
+  </si>
+  <si>
+    <t>Fear of losing their "expert" status</t>
+  </si>
+  <si>
+    <t>Access to Beta/New Tech</t>
+  </si>
+  <si>
+    <t>Access to Skilled Experts (Product/Eng)</t>
+  </si>
+  <si>
+    <t>Flexible, open platform (APIs)</t>
+  </si>
+  <si>
+    <t>Community forum/engagement</t>
+  </si>
+  <si>
+    <t>Pushing technical limits</t>
+  </si>
+  <si>
+    <t>Personal recognition as a thought leader</t>
+  </si>
+  <si>
+    <t>Future-Proofing their skills/company</t>
+  </si>
+  <si>
+    <t>Solving novel problems</t>
+  </si>
+  <si>
+    <t>"Black Box" approaches; demands Explainability</t>
+  </si>
+  <si>
+    <t>Lack of deep customization/control</t>
+  </si>
+  <si>
+    <t>Ethical &amp; Bias Issues</t>
+  </si>
+  <si>
+    <t>Closed, proprietary systems</t>
+  </si>
+  <si>
+    <t>Actionable Analytics &amp; Reporting</t>
+  </si>
+  <si>
+    <t>Data Export/Integration Capabilities</t>
+  </si>
+  <si>
+    <t>High accuracy and reliability</t>
+  </si>
+  <si>
+    <t>Customization of reports/dashboards</t>
+  </si>
+  <si>
+    <t>Ease of Use (for data tasks)</t>
+  </si>
+  <si>
+    <t>Enabling data-driven culture</t>
+  </si>
+  <si>
+    <t>Personal credibility as an analyst</t>
+  </si>
+  <si>
+    <t>Simplifying data complexity</t>
+  </si>
+  <si>
+    <t>Finding the "story" in the data</t>
+  </si>
+  <si>
+    <t>Risk of Inaccurate Outputs (Garbage-in, Gospel-out)</t>
+  </si>
+  <si>
+    <t>Lack of Explainability (how was this calculated?)</t>
+  </si>
+  <si>
+    <t>Potential for Bias in models</t>
+  </si>
+  <si>
+    <t>My data used for training other models</t>
+  </si>
+  <si>
+    <t>Enhanced Security &amp; Compliance</t>
+  </si>
+  <si>
+    <t>Auditable Logs &amp; Reporting</t>
+  </si>
+  <si>
+    <t>Data Encryption &amp; Controls</t>
+  </si>
+  <si>
+    <t>Fast patching of vulnerabilities</t>
+  </si>
+  <si>
+    <t>Mitigating Business &amp; Security Risk</t>
+  </si>
+  <si>
+    <t>Ensuring company-wide compliance</t>
+  </si>
+  <si>
+    <t>Standardization of security processes</t>
+  </si>
+  <si>
+    <t>Personal responsibility to protect the company</t>
+  </si>
+  <si>
+    <t>Avoiding a career-ending breach</t>
+  </si>
+  <si>
+    <t>Data Sovereignty &amp; Residency Laws</t>
+  </si>
+  <si>
+    <t>Lack of Explainability &amp; Auditability</t>
+  </si>
+  <si>
+    <t>New AI-specific attack vectors</t>
+  </si>
+  <si>
+    <t>Reliability (Don't change what works)</t>
+  </si>
+  <si>
+    <t>No disruption to their workflow</t>
+  </si>
+  <si>
+    <t>Seamless Integration (if forced to change)</t>
+  </si>
+  <si>
+    <t>Long-term support for existing tools</t>
+  </si>
+  <si>
+    <t>No forced upgrades</t>
+  </si>
+  <si>
+    <t>Mitigating Personal Disruption &amp; Risk</t>
+  </si>
+  <si>
+    <t>Maintaining their current expertise</t>
+  </si>
+  <si>
+    <t>Simplifying their own job</t>
+  </si>
+  <si>
+    <t>If it ain't broke, don't fix it</t>
+  </si>
+  <si>
+    <t>Avoiding the pain of change management</t>
+  </si>
+  <si>
+    <t>High Effort to learn/implement</t>
+  </si>
+  <si>
+    <t>Unclear ROI (Why change?)</t>
+  </si>
+  <si>
+    <t>Integration Complexity with tools they like</t>
+  </si>
+  <si>
+    <t>Don't trust the new "magic"</t>
+  </si>
+  <si>
+    <t>Continued support for their system</t>
+  </si>
+  <si>
+    <t>Interoperability with their system</t>
+  </si>
+  <si>
+    <t>Acknowledgment of their expertise</t>
+  </si>
+  <si>
+    <t>No forced migration</t>
+  </si>
+  <si>
+    <t>Reliability</t>
+  </si>
+  <si>
+    <t>Protecting their job security &amp; expertise</t>
+  </si>
+  <si>
+    <t>Mitigating risk of a failed migration</t>
+  </si>
+  <si>
+    <t>Maintaining control over their domain</t>
+  </si>
+  <si>
+    <t>Belief that their system is superior</t>
+  </si>
+  <si>
+    <t>Avoiding the pain of retraining</t>
+  </si>
+  <si>
+    <t>Fear of Job Displacement / Obsolescence</t>
+  </si>
+  <si>
+    <t>Threatens their core expertise</t>
+  </si>
+  <si>
+    <t>Integration Complexity with their legacy system</t>
+  </si>
+  <si>
+    <t>High cost compared to "free" legacy system</t>
+  </si>
+  <si>
+    <t>AI is unproven vs their time-tested system</t>
+  </si>
+  <si>
+    <t>Actionable Analytics for their clients</t>
+  </si>
+  <si>
+    <t>Strong case studies and ROI proof</t>
+  </si>
+  <si>
+    <t>Co-marketing opportunities</t>
+  </si>
+  <si>
+    <t>Reliability &amp; Security (protects their rep)</t>
+  </si>
+  <si>
+    <t>Personal credibility with clients</t>
+  </si>
+  <si>
+    <t>Growing their own business</t>
+  </si>
+  <si>
+    <t>Demonstrating Innovation to clients</t>
+  </si>
+  <si>
+    <t>Gaining a competitive edge</t>
+  </si>
+  <si>
+    <t>Simplifying client problems</t>
+  </si>
+  <si>
+    <t>Unclear ROI (Can't recommend to client)</t>
+  </si>
+  <si>
+    <t>Lack of Explainability (Can't defend to client)</t>
+  </si>
+  <si>
+    <t>IP &amp; Data Ownership (Client's data)</t>
+  </si>
+  <si>
+    <t>Risk of failed implementation (Damages their rep)</t>
+  </si>
+  <si>
+    <t>High Cost for their client</t>
+  </si>
+  <si>
+    <t>Dedicated partner support &amp; training</t>
+  </si>
+  <si>
+    <t>Customization &amp; Integration (APIs)</t>
+  </si>
+  <si>
+    <t>Predictable product roadmap</t>
+  </si>
+  <si>
+    <t>Fair partner commercial model</t>
+  </si>
+  <si>
+    <t>Growing their own services revenue</t>
+  </si>
+  <si>
+    <t>Simplifying their implementation work</t>
+  </si>
+  <si>
+    <t>Becoming a trusted expert on your platform</t>
+  </si>
+  <si>
+    <t>Mitigating project risk &amp; failure</t>
+  </si>
+  <si>
+    <t>Attracting/retaining skilled talent</t>
+  </si>
+  <si>
+    <t>High Implementation Effort for AI</t>
+  </si>
+  <si>
+    <t>Lack of skills on their team</t>
+  </si>
+  <si>
+    <t>Lack of Explainability (Hard to troubleshoot)</t>
+  </si>
+  <si>
+    <t>Unclear who is liable if AI fails</t>
+  </si>
+  <si>
+    <t>Stable, well-documented APIs</t>
+  </si>
+  <si>
+    <t>Developer sandbox/environment</t>
+  </si>
+  <si>
+    <t>Good developer support</t>
+  </si>
+  <si>
+    <t>Fair API usage/pricing model</t>
+  </si>
+  <si>
+    <t>Access to new AI models via API</t>
+  </si>
+  <si>
+    <t>Building a successful product/business</t>
+  </si>
+  <si>
+    <t>Simplifying their development work</t>
+  </si>
+  <si>
+    <t>Gaining a competitive advantage</t>
+  </si>
+  <si>
+    <t>Future-proofing their application</t>
+  </si>
+  <si>
+    <t>Solving a customer need</t>
+  </si>
+  <si>
+    <t>API Instability or breaking changes</t>
+  </si>
+  <si>
+    <t>High cost of AI API calls</t>
+  </si>
+  <si>
+    <t>IP &amp; Data Ownership of app &amp; data</t>
+  </si>
+  <si>
+    <t>"Black Box" APIs are hard to build on</t>
+  </si>
+  <si>
+    <t>Rate limiting and performance issues</t>
+  </si>
+  <si>
+    <t>Enhanced Compliance &amp; Auditing</t>
+  </si>
+  <si>
+    <t>Detailed reporting</t>
+  </si>
+  <si>
+    <t>Adherence to standards (ISO, SOC2 etc)</t>
+  </si>
+  <si>
+    <t>Data residency/sovereignty controls</t>
+  </si>
+  <si>
+    <t>Reliability &amp; Security</t>
+  </si>
+  <si>
+    <t>Mitigating Business &amp; Regulatory Risk</t>
+  </si>
+  <si>
+    <t>Simplifying the audit process</t>
+  </si>
+  <si>
+    <t>Personal responsibility to avoid fines/penalties</t>
+  </si>
+  <si>
+    <t>Standardization of processes</t>
+  </si>
+  <si>
+    <t>Potential for Bias &amp; Ethical Issues</t>
+  </si>
+  <si>
+    <t>Multi-region/language/currency support</t>
+  </si>
+  <si>
+    <t>Centralized reporting &amp; analytics</t>
+  </si>
+  <si>
+    <t>Standardization of tools &amp; workflows</t>
+  </si>
+  <si>
+    <t>Simplifying global complexity</t>
+  </si>
+  <si>
+    <t>IT-Business Alignment across regions</t>
+  </si>
+  <si>
+    <t>Mitigating operational/regional risk</t>
+  </si>
+  <si>
+    <t>Gaining a single source of truth</t>
+  </si>
+  <si>
+    <t>Integration with regional legacy systems</t>
+  </si>
+  <si>
+    <t>Varying global regulations for AI</t>
+  </si>
+  <si>
+    <t>Lack of skills in different regions</t>
+  </si>
+  <si>
+    <t>High cost to implement globally</t>
+  </si>
+  <si>
+    <t>Data Privacy &amp; Security Risks (Top Concern)</t>
+  </si>
+  <si>
+    <t>Fear of Job Displacement (Top Concern)</t>
+  </si>
+  <si>
+    <t>Regulatory &amp; Compliance Uncertainty (Top Concern)</t>
+  </si>
+  <si>
+    <t>Data Sovereignty &amp; Residency Laws (Top Concern)</t>
+  </si>
+  <si>
+    <t>The archetype's specific role and influence within the committee that approves a purchase.</t>
+  </si>
+  <si>
+    <t>The intensity of the competitive environment the archetype's company operates within.</t>
+  </si>
+  <si>
+    <t>The level of regulatory scrutiny the archetype's organization is under, which dictates their risk tolerance.</t>
+  </si>
+  <si>
+    <t>AI/GenAI Stance</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>AI Enthusiast</t>
+  </si>
+  <si>
+    <t>Show me how GenAI can Wan to disrupt industry. Want to be first.</t>
+  </si>
+  <si>
+    <t>AI Pragmatist</t>
+  </si>
+  <si>
+    <t>Show me a clear ROI and a specific use case that solves my problem todaywe must discuss data privacy, bias, and governance." &lt;br&gt; 5. AI Laggard: "We are not ready for this. Our basic data infrastructure isn't even in place."</t>
+  </si>
+  <si>
+    <t>AI Skeptic</t>
+  </si>
+  <si>
+    <t>This feels like hype. I'm concerned about the risks, costs, and unproven nature of this.</t>
+  </si>
+  <si>
+    <t>AI Ethicist</t>
+  </si>
+  <si>
+    <t>Before we discuss features, we must discuss data privacy, bias, and governance</t>
+  </si>
+  <si>
+    <t>AI Laggard</t>
+  </si>
+  <si>
+    <t>We are not ready for this. Our basic data infrastructure isn't even in place</t>
+  </si>
+  <si>
+    <t>Strategic Partner</t>
+  </si>
+  <si>
+    <t>You are our go-to for innovation. What should we be doing next together?</t>
+  </si>
+  <si>
+    <t>Primary Vendor</t>
+  </si>
+  <si>
+    <t>Secondary/Niche Vendor</t>
+  </si>
+  <si>
+    <t>You solve one specific problem for us. We only engage when we have to</t>
+  </si>
+  <si>
+    <t>You are critical to our operations. We need reliability and excellent support above all</t>
+  </si>
+  <si>
+    <t>New Prospect</t>
+  </si>
+  <si>
+    <t>We don't know you. You have to earn our trust and prove your value from scratch.</t>
+  </si>
+  <si>
+    <t>Ex-Customer / Churned</t>
+  </si>
+  <si>
+    <t>You failed us in the past. We are highly skeptical of any new promises</t>
+  </si>
+  <si>
+    <t>The Innovators</t>
+  </si>
+  <si>
+    <t>We come to you for cutting-edge ideas, but worry about your execution at scale</t>
+  </si>
+  <si>
+    <t>The Safe Pair of Hands</t>
+  </si>
+  <si>
+    <t>We trust you to deliver, but you are slow and not very creative</t>
+  </si>
+  <si>
+    <t>The Low-Cost Option</t>
+  </si>
+  <si>
+    <t>You are great for saving us money, but we don't trust you with mission-critical work</t>
+  </si>
+  <si>
+    <t>The Technical Gurus</t>
+  </si>
+  <si>
+    <t>Your engineers are brilliant, but your project management and communication are poor</t>
+  </si>
+  <si>
+    <t>The Relationship Experts</t>
+  </si>
+  <si>
+    <t>Your account managers are fantastic, but your underlying technology feels dated.</t>
+  </si>
+  <si>
+    <t>Geographic &amp; Cultural Context</t>
+  </si>
+  <si>
+    <t>Emphasis on data privacy (GDPR), quality engineering, and consensus-based decisions</t>
+  </si>
+  <si>
+    <t>Emphasis on flat hierarchies, sustainability, design, and work-life balance.</t>
+  </si>
+  <si>
+    <t>Emphasis on long-term relationships, risk aversion, and harmony-seeking communication</t>
+  </si>
+  <si>
+    <t>Emphasis on mobile-first solutions, scalability, and value-for-money.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Company Maturity &amp; Scale</t>
+  </si>
+  <si>
+    <t>The size, age, and internal process maturity of the archetype's organization</t>
+  </si>
+  <si>
+    <t>Startup</t>
+  </si>
+  <si>
+    <t>Processes are chaotic; speed and flexibility are paramount</t>
+  </si>
+  <si>
+    <t>High-Growth Scale-Up</t>
+  </si>
+  <si>
+    <t>Processes are being built; struggling with technical debt and scaling challenges</t>
+  </si>
+  <si>
+    <t>Established Mid-Market</t>
+  </si>
+  <si>
+    <t>Processes are defined but can be rigid; balancing growth with stability.</t>
+  </si>
+  <si>
+    <t>Large Enterprise</t>
+  </si>
+  <si>
+    <t>Processes are complex and siloed; navigating bureaucracy is a key challenge.</t>
+  </si>
+  <si>
+    <t>Legacy Incumbent</t>
+  </si>
+  <si>
+    <t>Processes are deeply entrenched; high resistance to change and significant legacy tech.</t>
+  </si>
+  <si>
+    <t>Digital Transformation Stage</t>
+  </si>
+  <si>
+    <t>To provide an AI solution that matches their current capacity and appetite for technological change.</t>
+  </si>
+  <si>
+    <t>Digital Native</t>
+  </si>
+  <si>
+    <t>Born with modern tech; expects seamless, API-driven solutions</t>
+  </si>
+  <si>
+    <t>Actively investing in and executing a company-wide transformation strategy.</t>
+  </si>
+  <si>
+    <t>Digital Adopter</t>
+  </si>
+  <si>
+    <t>Implementing digital solutions on a project-by-project basis, not strategically.</t>
+  </si>
+  <si>
+    <t>Digital Laggard</t>
+  </si>
+  <si>
+    <t>Acknowledges the need for change but is slow to act due to culture or cost.</t>
+  </si>
+  <si>
+    <t>Transformation Distress:</t>
+  </si>
+  <si>
+    <t>A past transformation effort failed, leading to high skepticism and fatigue.</t>
+  </si>
+  <si>
+    <t>Buying Center Role</t>
+  </si>
+  <si>
+    <t>Economic Buyer</t>
+  </si>
+  <si>
+    <t>Holds the ultimate budget and is focused on financial ROI and TCO</t>
+  </si>
+  <si>
+    <t>User Buyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Represents the end-users and is focused on usability and day-to-day functionality. </t>
+  </si>
+  <si>
+    <t>Technical Buyer</t>
+  </si>
+  <si>
+    <t>Evaluates the solution against security, integration, and architecture standards.</t>
+  </si>
+  <si>
+    <t>Champion</t>
+  </si>
+  <si>
+    <t>Does not hold the budget but advocates for your solution internally</t>
+  </si>
+  <si>
+    <t>Blocker / Saboteur</t>
+  </si>
+  <si>
+    <t>Actively works against the deal, often to protect their own role or preferred vendor.</t>
+  </si>
+  <si>
+    <t>Competitive Pressure</t>
+  </si>
+  <si>
+    <t>Focus on maintaining their dominant position and optimizing efficiency</t>
+  </si>
+  <si>
+    <t>Market Leader</t>
+  </si>
+  <si>
+    <t>Aggressive Challenger</t>
+  </si>
+  <si>
+    <t>Focus on disruption and gaining market share; willing to take risks.</t>
+  </si>
+  <si>
+    <t>Niche Specialist</t>
+  </si>
+  <si>
+    <t>Focus on defending their specialized market from larger players.</t>
+  </si>
+  <si>
+    <t>Commoditized Follower</t>
+  </si>
+  <si>
+    <t>Focus on cost-cutting and survival in a low-margin environment.</t>
+  </si>
+  <si>
+    <t>Regulated Monopoly</t>
+  </si>
+  <si>
+    <t>Focus on compliance and stability, with little competitive threat.</t>
+  </si>
+  <si>
+    <t>Regulatory &amp; Compliance Posture</t>
+  </si>
+  <si>
+    <t>Heavily Regulated</t>
+  </si>
+  <si>
+    <t>(e.g., Banking, Pharma) Compliance is a non-negotiable, top-down mandate.</t>
+  </si>
+  <si>
+    <t>Data-Sensitive</t>
+  </si>
+  <si>
+    <t>(e.g., B2C Retail) Not heavily regulated, but highly sensitive to customer data privacy due to brand risk.</t>
+  </si>
+  <si>
+    <t>Industry Standard-Driven</t>
+  </si>
+  <si>
+    <t>(e.g., ISO, SOC2) Adheres to standards as a mark of quality and to meet partner requirements</t>
+  </si>
+  <si>
+    <t>Self-Regulated</t>
+  </si>
+  <si>
+    <t>Operates with an internal code of ethics but lacks external oversight.</t>
+  </si>
+  <si>
+    <t>Unregulated Frontier</t>
+  </si>
+  <si>
+    <t>(e.g., some startups) Operates in a new space with few established rules, prioritizing growth over compliance.</t>
+  </si>
+  <si>
+    <t>Emphasis on speed-to-market, shareholder value, and a direct communication style, drive for commercialization</t>
+  </si>
+  <si>
+    <t>Digital Transformer</t>
+  </si>
+  <si>
+    <t>North America</t>
+  </si>
+  <si>
+    <t>Europe</t>
+  </si>
+  <si>
+    <t>Asia-Pacific</t>
+  </si>
+  <si>
+    <t>Growth Markets</t>
+  </si>
+  <si>
+    <t>Attitude and readiness towards adopting AI</t>
+  </si>
+  <si>
+    <t>Current perception and status of TCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How archetype perceives TCS </t>
+  </si>
+  <si>
+    <t>The regional and cultural norms that influence decision-making, and priorities.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -339,16 +1535,55 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1B1C1D"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1B1C1D"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF1B1C1D"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0095B6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6F8FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -356,11 +1591,57 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -368,12 +1649,70 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFC6F8FF"/>
+      <color rgb="FF0095B6"/>
+      <color rgb="FF468FEA"/>
+      <color rgb="FF2DC8FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -659,21 +1998,21 @@
     <col min="6" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" s="2" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>49</v>
+      <c r="E1" s="9" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -684,13 +2023,13 @@
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -698,13 +2037,13 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -712,27 +2051,28 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>57</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -740,16 +2080,16 @@
         <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -757,27 +2097,28 @@
         <v>9</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>63</v>
+      <c r="C8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -788,13 +2129,13 @@
         <v>12</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -802,13 +2143,13 @@
         <v>13</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -816,27 +2157,28 @@
         <v>14</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>71</v>
+      <c r="C12" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -847,13 +2189,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -861,27 +2203,28 @@
         <v>18</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>77</v>
+      <c r="C15" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -892,69 +2235,70 @@
         <v>21</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>87</v>
+      <c r="C20" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -963,6 +2307,2118 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00CFFB1A-CB9D-44BF-9B18-AF962240F08D}">
+  <dimension ref="A1:E66"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.109375" style="22" customWidth="1"/>
+    <col min="4" max="4" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="72.33203125" style="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="2" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>466</v>
+      </c>
+      <c r="D2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="19"/>
+      <c r="D3" t="s">
+        <v>371</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="19"/>
+      <c r="D4" t="s">
+        <v>373</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="19"/>
+      <c r="D5" t="s">
+        <v>375</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="1" customFormat="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>467</v>
+      </c>
+      <c r="D7" t="s">
+        <v>379</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="19"/>
+      <c r="D8" t="s">
+        <v>381</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="19"/>
+      <c r="D9" t="s">
+        <v>382</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="19"/>
+      <c r="D10" t="s">
+        <v>385</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" s="1" customFormat="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="B12" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>468</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="14"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="15" t="s">
+        <v>391</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="14"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="14"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" s="1" customFormat="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="16" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="14"/>
+      <c r="B17" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>469</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>462</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="16" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="14"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="15" t="s">
+        <v>463</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="14"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="16" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="14"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="15" t="s">
+        <v>464</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="1" customFormat="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="16" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="14"/>
+      <c r="B22" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>405</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="14"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="14"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="14"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="15" t="s">
+        <v>412</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" s="1" customFormat="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" s="16" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="14"/>
+      <c r="B27" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>417</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="14"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="15" t="s">
+        <v>461</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="14"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="15" t="s">
+        <v>421</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="14"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="15" t="s">
+        <v>423</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="1" customFormat="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="16" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="14"/>
+      <c r="B32" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>363</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="14"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="14"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="14"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" s="1" customFormat="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="8"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8" t="s">
+        <v>436</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" s="16" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="14"/>
+      <c r="B37" s="15" t="s">
+        <v>438</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>364</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="14"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="14"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="14"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="15" t="s">
+        <v>445</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" s="1" customFormat="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="8"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" s="16" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="14"/>
+      <c r="B42" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>450</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" s="16" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="14"/>
+      <c r="B43" s="15"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="E43" s="20" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" s="16" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="14"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="15" t="s">
+        <v>454</v>
+      </c>
+      <c r="E44" s="20" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="14"/>
+      <c r="B45" s="15"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="15" t="s">
+        <v>456</v>
+      </c>
+      <c r="E45" s="20" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" s="1" customFormat="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="8"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="14"/>
+      <c r="B47" s="15"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="20"/>
+    </row>
+    <row r="48" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="14"/>
+      <c r="B48" s="15"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="20"/>
+    </row>
+    <row r="49" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="14"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="20"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="20"/>
+    </row>
+    <row r="50" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="14"/>
+      <c r="B50" s="15"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="20"/>
+    </row>
+    <row r="51" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="14"/>
+      <c r="B51" s="15"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="20"/>
+    </row>
+    <row r="52" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="14"/>
+      <c r="B52" s="15"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="20"/>
+    </row>
+    <row r="53" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="14"/>
+      <c r="B53" s="15"/>
+      <c r="C53" s="20"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="20"/>
+    </row>
+    <row r="54" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="14"/>
+      <c r="B54" s="15"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="20"/>
+    </row>
+    <row r="55" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="14"/>
+      <c r="B55" s="15"/>
+      <c r="C55" s="20"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="20"/>
+    </row>
+    <row r="56" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="14"/>
+      <c r="B56" s="15"/>
+      <c r="C56" s="20"/>
+      <c r="D56" s="15"/>
+      <c r="E56" s="20"/>
+    </row>
+    <row r="57" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="14"/>
+      <c r="B57" s="15"/>
+      <c r="C57" s="20"/>
+      <c r="D57" s="15"/>
+      <c r="E57" s="20"/>
+    </row>
+    <row r="58" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="14"/>
+      <c r="B58" s="15"/>
+      <c r="C58" s="20"/>
+      <c r="D58" s="15"/>
+      <c r="E58" s="20"/>
+    </row>
+    <row r="59" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A59" s="14"/>
+      <c r="B59" s="15"/>
+      <c r="C59" s="20"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="20"/>
+    </row>
+    <row r="60" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="14"/>
+      <c r="B60" s="15"/>
+      <c r="C60" s="20"/>
+      <c r="D60" s="15"/>
+      <c r="E60" s="20"/>
+    </row>
+    <row r="61" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A61" s="14"/>
+      <c r="B61" s="15"/>
+      <c r="C61" s="20"/>
+      <c r="D61" s="15"/>
+      <c r="E61" s="20"/>
+    </row>
+    <row r="62" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="14"/>
+      <c r="B62" s="15"/>
+      <c r="C62" s="20"/>
+      <c r="D62" s="15"/>
+      <c r="E62" s="20"/>
+    </row>
+    <row r="63" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A63" s="14"/>
+      <c r="B63" s="15"/>
+      <c r="C63" s="20"/>
+      <c r="D63" s="15"/>
+      <c r="E63" s="20"/>
+    </row>
+    <row r="64" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C64" s="21"/>
+      <c r="E64" s="21"/>
+    </row>
+    <row r="65" spans="3:5" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C65" s="21"/>
+      <c r="E65" s="21"/>
+    </row>
+    <row r="66" spans="3:5" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C66" s="21"/>
+      <c r="E66" s="21"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AEDF38F-70E2-4C23-91BE-1FF4EABB7EE9}">
+  <dimension ref="A1:E105"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="43.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+    </row>
+    <row r="4" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+    </row>
+    <row r="5" spans="1:5" s="2" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="6"/>
+      <c r="B11" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="6"/>
+      <c r="B16" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="6"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="6"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="6"/>
+      <c r="B21" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="6"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="6"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="6"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="6"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="6"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="6"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="6"/>
+      <c r="B31" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="6"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="6"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="6"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="6"/>
+      <c r="B36" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="6"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="6"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="6"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="7"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="6"/>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="6"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="6"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="6"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="6"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="6"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="6"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="7"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="6"/>
+      <c r="B51" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="6"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="6"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="6"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="7"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="6"/>
+      <c r="B56" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="6"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="6"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="6"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="7"/>
+      <c r="B60" s="7"/>
+      <c r="C60" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="6"/>
+      <c r="B61" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="6"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="6"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="6"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="7"/>
+      <c r="B65" s="7"/>
+      <c r="C65" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="6"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="6"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" s="6"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="7"/>
+      <c r="B70" s="7"/>
+      <c r="C70" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="6"/>
+      <c r="B71" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="6"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="6"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="6"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="7"/>
+      <c r="B75" s="7"/>
+      <c r="C75" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="6"/>
+      <c r="B76" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="6"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="6"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="6"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="7"/>
+      <c r="B80" s="7"/>
+      <c r="C80" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" s="6"/>
+      <c r="B82" s="5"/>
+      <c r="C82" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" s="6"/>
+      <c r="B83" s="5"/>
+      <c r="C83" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" s="6"/>
+      <c r="B84" s="5"/>
+      <c r="C84" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="7"/>
+      <c r="B85" s="7"/>
+      <c r="C85" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="E85" s="8" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86" s="6"/>
+      <c r="B86" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87" s="6"/>
+      <c r="B87" s="5"/>
+      <c r="C87" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" s="6"/>
+      <c r="B88" s="5"/>
+      <c r="C88" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89" s="6"/>
+      <c r="B89" s="5"/>
+      <c r="C89" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="7"/>
+      <c r="B90" s="7"/>
+      <c r="C90" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" s="6"/>
+      <c r="B91" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" s="6"/>
+      <c r="B92" s="5"/>
+      <c r="C92" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" s="6"/>
+      <c r="B93" s="5"/>
+      <c r="C93" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" s="6"/>
+      <c r="B94" s="5"/>
+      <c r="C94" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="7"/>
+      <c r="B95" s="7"/>
+      <c r="C95" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" s="6"/>
+      <c r="B96" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" s="6"/>
+      <c r="B97" s="5"/>
+      <c r="C97" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" s="6"/>
+      <c r="B98" s="5"/>
+      <c r="C98" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" s="6"/>
+      <c r="B99" s="5"/>
+      <c r="C99" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="7"/>
+      <c r="B100" s="7"/>
+      <c r="C100" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A101" s="6"/>
+      <c r="B101" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C102" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C103" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C104" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="7"/>
+      <c r="B105" s="7"/>
+      <c r="C105" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="D105" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E105" s="8" t="s">
+        <v>358</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55841D51-0A9A-488F-AC9D-07EF912AF8EC}">
   <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="13.95" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -992,31 +4448,31 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1027,13 +4483,13 @@
         <v>4</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F3" s="4">
         <v>0.2</v>
@@ -1041,16 +4497,16 @@
     </row>
     <row r="4" spans="1:11" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F4" s="4">
         <v>0.4</v>
@@ -1061,13 +4517,13 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F5" s="4">
         <v>0.4</v>
@@ -1078,13 +4534,13 @@
         <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F6" s="4">
         <v>0.1</v>
@@ -1095,16 +4551,16 @@
         <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1112,13 +4568,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1126,13 +4582,13 @@
         <v>10</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1143,13 +4599,13 @@
         <v>12</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1157,13 +4613,13 @@
         <v>13</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1171,13 +4627,13 @@
         <v>14</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1185,13 +4641,13 @@
         <v>15</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1202,13 +4658,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1216,13 +4672,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1230,13 +4686,13 @@
         <v>19</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1247,13 +4703,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1261,13 +4717,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1275,13 +4731,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1289,13 +4745,13 @@
         <v>24</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1303,85 +4759,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00CFFB1A-CB9D-44BF-9B18-AF962240F08D}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="97.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/Dimensions.xlsx
+++ b/Dimensions.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\08-MyCOOCharter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB85AA3-148F-4E19-80CF-5741B58282DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9201EFE4-FCA5-454A-B952-175627538B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CustomerArchetype" sheetId="1" r:id="rId1"/>
     <sheet name="EnhancedArchitypeStructure" sheetId="2" r:id="rId2"/>
     <sheet name="WhatWhyWhynot" sheetId="5" r:id="rId3"/>
-    <sheet name="CustomerArchetype-Instantiation" sheetId="4" r:id="rId4"/>
+    <sheet name="Proposals-Eval" sheetId="6" r:id="rId4"/>
+    <sheet name="CustomerArchetype-Instantiation" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="586">
   <si>
     <t>Archetype Bucket</t>
   </si>
@@ -1509,12 +1510,381 @@
   <si>
     <t>The regional and cultural norms that influence decision-making, and priorities.</t>
   </si>
+  <si>
+    <t>Dimension</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>Scoring</t>
+  </si>
+  <si>
+    <t>Scoring Type</t>
+  </si>
+  <si>
+    <t>Customer Fit &amp; Business Alignment</t>
+  </si>
+  <si>
+    <t>Problem Alignment</t>
+  </si>
+  <si>
+    <t>How well the proposal aligns with the customer's pain points and strategic priorities.</t>
+  </si>
+  <si>
+    <t>Qualitative (1-5)</t>
+  </si>
+  <si>
+    <t>Industry Relevance</t>
+  </si>
+  <si>
+    <t>Whether the use cases proposed are tailored to the customer’s industry.</t>
+  </si>
+  <si>
+    <t>AI/GenAI Value Proposition</t>
+  </si>
+  <si>
+    <t>Is the AI/GenAI component clearly linked to measurable business outcomes (e.g., cost savings, speed)?</t>
+  </si>
+  <si>
+    <t>Customization Level</t>
+  </si>
+  <si>
+    <t>Degree to which the solution was tailored vs. generic.</t>
+  </si>
+  <si>
+    <t>Stakeholder Mapping</t>
+  </si>
+  <si>
+    <t>Technical Strength</t>
+  </si>
+  <si>
+    <t>Feasibility of AI/GenAI Solution</t>
+  </si>
+  <si>
+    <t>Are the proposed models, architecture, and integrations practical and implementable?</t>
+  </si>
+  <si>
+    <t>Can the solution scale with customer growth?</t>
+  </si>
+  <si>
+    <t>Data Readiness</t>
+  </si>
+  <si>
+    <t>Model Selection &amp; Rationale</t>
+  </si>
+  <si>
+    <t>Clarity on why specific AI/GenAI techniques were chosen.</t>
+  </si>
+  <si>
+    <t>Ease of integrating into existing customer systems.</t>
+  </si>
+  <si>
+    <t>Innovation &amp; Differentiation</t>
+  </si>
+  <si>
+    <t>Use of Emerging AI Techniques</t>
+  </si>
+  <si>
+    <t>IP or Accelerators</t>
+  </si>
+  <si>
+    <t>Differentiators vs. Competitors</t>
+  </si>
+  <si>
+    <t>Was the GenAI aspect positioned as a unique advantage?</t>
+  </si>
+  <si>
+    <t>Personalization in AI Outputs</t>
+  </si>
+  <si>
+    <t>Visionary Value</t>
+  </si>
+  <si>
+    <t>Long-term transformational impact proposed by the AI component.</t>
+  </si>
+  <si>
+    <t>Commercial Viability</t>
+  </si>
+  <si>
+    <t>Pricing Competitiveness</t>
+  </si>
+  <si>
+    <t>Overall cost competitiveness, especially of AI/GenAI component.</t>
+  </si>
+  <si>
+    <t>ROI Justification</t>
+  </si>
+  <si>
+    <t>Tangible value vs. cost of GenAI features (e.g., automation savings).</t>
+  </si>
+  <si>
+    <t>Flexibility in Commercial Models</t>
+  </si>
+  <si>
+    <t>Outcome-based pricing, pay-as-you-use, etc.</t>
+  </si>
+  <si>
+    <t>Licensing and Platform Costs</t>
+  </si>
+  <si>
+    <t>Clarity on GenAI model/API licensing costs.</t>
+  </si>
+  <si>
+    <t>TCO &amp; Long-Term Commitments</t>
+  </si>
+  <si>
+    <t>Total cost over 2-5 years including updates, fine-tuning, infra.</t>
+  </si>
+  <si>
+    <t>Trust, Risk, and Governance</t>
+  </si>
+  <si>
+    <t>Addressed concerns on explainability, fairness, and hallucinations.</t>
+  </si>
+  <si>
+    <t>Security &amp; Compliance</t>
+  </si>
+  <si>
+    <t>Auditability &amp; Traceability</t>
+  </si>
+  <si>
+    <t>Is the AI decisioning auditable and logged?</t>
+  </si>
+  <si>
+    <t>Model Lifecycle Management</t>
+  </si>
+  <si>
+    <t>Plans for monitoring, updating, and retraining models.</t>
+  </si>
+  <si>
+    <t>Risk Management Strategy</t>
+  </si>
+  <si>
+    <t>Proposal Quality &amp; Delivery Readiness</t>
+  </si>
+  <si>
+    <t>Clarity &amp; Structure</t>
+  </si>
+  <si>
+    <t>How well the proposal articulates the problem, solution, and value.</t>
+  </si>
+  <si>
+    <t>AI/GenAI Storytelling</t>
+  </si>
+  <si>
+    <t>Was the AI journey made relatable and compelling?</t>
+  </si>
+  <si>
+    <t>Past Credentials / Case Studies</t>
+  </si>
+  <si>
+    <t>Relevant success stories in similar industries.</t>
+  </si>
+  <si>
+    <t>Team Capability</t>
+  </si>
+  <si>
+    <t>Strength of the delivery team, especially in AI/GenAI.</t>
+  </si>
+  <si>
+    <t>Timeline &amp; Execution Plan</t>
+  </si>
+  <si>
+    <t>Did the proposal address the key decision-makers and influencers? (CxO, Ops, IT, etc.)</t>
+  </si>
+  <si>
+    <t>Business Goal Alignment</t>
+  </si>
+  <si>
+    <t>Degree to which the proposal fit with customer's near/mid-term strategic objectives.</t>
+  </si>
+  <si>
+    <t>Customer Archetype</t>
+  </si>
+  <si>
+    <t>What is the archetype of the customer based on AI maturity (Explorer, Adopter, Leader) and innovation appetite.</t>
+  </si>
+  <si>
+    <t>MLOps and Lifecycle Plan</t>
+  </si>
+  <si>
+    <t>Has the proposal addresses mechanisms for monitoring, updating, and governing AI models.</t>
+  </si>
+  <si>
+    <t>ROI Projection</t>
+  </si>
+  <si>
+    <t>Business Impact</t>
+  </si>
+  <si>
+    <t>Value-for-money based on cost savings, growth, or productivity gains.</t>
+  </si>
+  <si>
+    <t>Process Efficiency Gain</t>
+  </si>
+  <si>
+    <t>Quantified impact on automation, speed, or accuracy.</t>
+  </si>
+  <si>
+    <t>Strategic Transformation Potential</t>
+  </si>
+  <si>
+    <t>Degree to which the proposal articulated the Long-term transformational potential of the AI solution.</t>
+  </si>
+  <si>
+    <t>CxO Strategic Leverage</t>
+  </si>
+  <si>
+    <t>Visibility and relevance to board-level or transformation agenda.</t>
+  </si>
+  <si>
+    <t>Deal Value</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Projected TCV of the deal. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color rgb="FFFF6969"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Higher value deals typically invite deeper scrutiny</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1B1C1D"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Uniqueness of Solution</t>
+  </si>
+  <si>
+    <t>Is the approach novel compared to competitors?</t>
+  </si>
+  <si>
+    <t>Use of LLMs, prompt engineering, RAG, agents, CoPilot, multi-agent systems, etc.</t>
+  </si>
+  <si>
+    <t>Proprietary frameworks, reusable components, pre-trained models offered. Internal tools, frameworks, or libraries proposed.</t>
+  </si>
+  <si>
+    <t>Has the proposal addressed the customer’s data landscape for AI readiness (quality, structure, availability).</t>
+  </si>
+  <si>
+    <t>Degree of contextual relevance to the customer. Ability to tailor outputs to end-user contexts dynamically.</t>
+  </si>
+  <si>
+    <t>Future-readiness</t>
+  </si>
+  <si>
+    <t>Extensibility for evolving GenAI capabilities (multimodal, real-time).</t>
+  </si>
+  <si>
+    <t>Partnership &amp; Ecosystem Strength</t>
+  </si>
+  <si>
+    <t>Hyperscaler Alignment</t>
+  </si>
+  <si>
+    <t>Did the proposal leverage strategic alignment with Microsoft, AWS, Google, etc.</t>
+  </si>
+  <si>
+    <t>Startup/LLM Partner</t>
+  </si>
+  <si>
+    <t>Did the proposal showcase named partnerships or co-development with AI startups or labs.</t>
+  </si>
+  <si>
+    <t>Delivery Alliances</t>
+  </si>
+  <si>
+    <t>Collaborations for scaling, governance, or deployment.</t>
+  </si>
+  <si>
+    <t>Co-Innovation Capability</t>
+  </si>
+  <si>
+    <t>Did the proposal showcase ability to jointly experiment with the customer.</t>
+  </si>
+  <si>
+    <t>Ecosystem Readiness</t>
+  </si>
+  <si>
+    <t>Did the proposal showcase the Strength of APIs, open standards, and plug-and-play integrations.</t>
+  </si>
+  <si>
+    <t>How AI data handling complies with GDPR, HIPAA, SOC2, EU AI Act etc.</t>
+  </si>
+  <si>
+    <t>Did the proposal and solution detail fallback/rollback plans, escalation, or human-in-the-loop systems.</t>
+  </si>
+  <si>
+    <t>AI Ethics,Bias, Explainability</t>
+  </si>
+  <si>
+    <t>Realistic milestones, agile sprints, PoC plans. Realism of proposed milestones.</t>
+  </si>
+  <si>
+    <t>Readiness for Scale</t>
+  </si>
+  <si>
+    <t>Degree of Clarity of roadmap from PoC to scaled deployment.</t>
+  </si>
+  <si>
+    <t>Demonstrations</t>
+  </si>
+  <si>
+    <t>Did the proposal offer demonstrations of TCS capabilities, tools, offerings, accelerators</t>
+  </si>
+  <si>
+    <t>Commercial Competitiveness</t>
+  </si>
+  <si>
+    <t>Pricing Strategy</t>
+  </si>
+  <si>
+    <t>What was the pricing model adopted for the proposal? Was it transparent and adaptable pricing.</t>
+  </si>
+  <si>
+    <t>TCO over Lifecycle</t>
+  </si>
+  <si>
+    <t>Did the proposal address Cost beyond implementation — retraining, infra, licenses.</t>
+  </si>
+  <si>
+    <t>Procurement Fit</t>
+  </si>
+  <si>
+    <t>Degree of alignment with customers vendor/contracting policies.</t>
+  </si>
+  <si>
+    <t>Negotiation Flexibility</t>
+  </si>
+  <si>
+    <t>Did the proposal offer willingness to co-create commercials (e.g., outcome-based).</t>
+  </si>
+  <si>
+    <t>Competitor Positioning</t>
+  </si>
+  <si>
+    <t>Were we aware of competing offers and differentiation from competitors</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1559,6 +1929,21 @@
       <b/>
       <sz val="10"/>
       <color theme="0"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8"/>
+      <color rgb="FFFF6969"/>
       <name val="Aptos"/>
       <family val="2"/>
     </font>
@@ -1641,7 +2026,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1670,34 +2055,33 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1707,6 +2091,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF6969"/>
       <color rgb="FFC6F8FF"/>
       <color rgb="FF0095B6"/>
       <color rgb="FF468FEA"/>
@@ -2308,14 +2693,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00CFFB1A-CB9D-44BF-9B18-AF962240F08D}">
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.109375" style="22" customWidth="1"/>
+    <col min="3" max="3" width="36.109375" style="15" customWidth="1"/>
     <col min="4" max="4" width="21.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="72.33203125" style="22" customWidth="1"/>
+    <col min="5" max="5" width="72.33203125" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="2" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2325,13 +2710,13 @@
       <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="12" t="s">
         <v>368</v>
       </c>
     </row>
@@ -2342,46 +2727,46 @@
       <c r="B2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="13" t="s">
         <v>466</v>
       </c>
       <c r="D2" t="s">
         <v>369</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="13" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="19"/>
+      <c r="C3" s="13"/>
       <c r="D3" t="s">
         <v>371</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="13" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
-      <c r="C4" s="19"/>
+      <c r="C4" s="13"/>
       <c r="D4" t="s">
         <v>373</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="13" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
-      <c r="C5" s="19"/>
+      <c r="C5" s="13"/>
       <c r="D5" t="s">
         <v>375</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="13" t="s">
         <v>376</v>
       </c>
     </row>
@@ -2397,52 +2782,52 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="13" t="s">
         <v>467</v>
       </c>
       <c r="D7" t="s">
         <v>379</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="13" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
-      <c r="C8" s="19"/>
+      <c r="C8" s="13"/>
       <c r="D8" t="s">
         <v>381</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="13" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
-      <c r="C9" s="19"/>
+      <c r="C9" s="13"/>
       <c r="D9" t="s">
         <v>382</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="13" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
-      <c r="C10" s="19"/>
+      <c r="C10" s="13"/>
       <c r="D10" t="s">
         <v>385</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="13" t="s">
         <v>386</v>
       </c>
     </row>
@@ -2457,50 +2842,50 @@
         <v>388</v>
       </c>
     </row>
-    <row r="12" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="15" t="s">
+    <row r="12" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="B12" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="14" t="s">
         <v>468</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="14" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="14"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="15" t="s">
+    <row r="13" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="5"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="14" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="14" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="14"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="15" t="s">
+    <row r="14" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="14" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="15" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="14"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="15" t="s">
+    <row r="15" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="14" t="s">
         <v>396</v>
       </c>
     </row>
@@ -2515,51 +2900,51 @@
         <v>398</v>
       </c>
     </row>
-    <row r="17" spans="1:5" s="16" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="14"/>
-      <c r="B17" s="15" t="s">
+    <row r="17" spans="1:5" s="1" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
+      <c r="B17" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="14" t="s">
         <v>469</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="6" t="s">
         <v>462</v>
       </c>
-      <c r="E17" s="20" t="s">
+      <c r="E17" s="14" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="18" spans="1:5" s="16" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="14"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="15" t="s">
+    <row r="18" spans="1:5" s="1" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="6" t="s">
         <v>463</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="E18" s="14" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="19" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="14"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="15" t="s">
+    <row r="19" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="5"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E19" s="20" t="s">
+      <c r="E19" s="14" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="20" spans="1:5" s="16" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="14"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="15" t="s">
+    <row r="20" spans="1:5" s="1" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="5"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="E20" s="14" t="s">
         <v>402</v>
       </c>
     </row>
@@ -2574,51 +2959,51 @@
         <v>403</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="16" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="14"/>
-      <c r="B22" s="15" t="s">
+    <row r="22" spans="1:5" s="1" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="5"/>
+      <c r="B22" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="E22" s="20" t="s">
+      <c r="E22" s="14" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="23" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="14"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="15" t="s">
+    <row r="23" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="5"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="E23" s="20" t="s">
+      <c r="E23" s="14" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="24" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="14"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="15" t="s">
+    <row r="24" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="5"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="E24" s="20" t="s">
+      <c r="E24" s="14" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="25" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="14"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="15" t="s">
+    <row r="25" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="5"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="6" t="s">
         <v>412</v>
       </c>
-      <c r="E25" s="20" t="s">
+      <c r="E25" s="14" t="s">
         <v>413</v>
       </c>
     </row>
@@ -2633,51 +3018,51 @@
         <v>415</v>
       </c>
     </row>
-    <row r="27" spans="1:5" s="16" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A27" s="14"/>
-      <c r="B27" s="15" t="s">
+    <row r="27" spans="1:5" s="1" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="5"/>
+      <c r="B27" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="C27" s="20" t="s">
+      <c r="C27" s="14" t="s">
         <v>417</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="E27" s="20" t="s">
+      <c r="E27" s="14" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="28" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="14"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="15" t="s">
+    <row r="28" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="5"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="E28" s="14" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="14"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="15" t="s">
+    <row r="29" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="5"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="6" t="s">
         <v>421</v>
       </c>
-      <c r="E29" s="20" t="s">
+      <c r="E29" s="14" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="30" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="14"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="15" t="s">
+    <row r="30" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="5"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="E30" s="20" t="s">
+      <c r="E30" s="14" t="s">
         <v>424</v>
       </c>
     </row>
@@ -2692,51 +3077,51 @@
         <v>426</v>
       </c>
     </row>
-    <row r="32" spans="1:5" s="16" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A32" s="14"/>
-      <c r="B32" s="15" t="s">
+    <row r="32" spans="1:5" s="1" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="5"/>
+      <c r="B32" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C32" s="14" t="s">
         <v>363</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="E32" s="20" t="s">
+      <c r="E32" s="14" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="33" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="14"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="15" t="s">
+    <row r="33" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="5"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="E33" s="20" t="s">
+      <c r="E33" s="14" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="34" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="14"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="15" t="s">
+    <row r="34" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="5"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="E34" s="20" t="s">
+      <c r="E34" s="14" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="35" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="14"/>
-      <c r="B35" s="15"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="15" t="s">
+    <row r="35" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="5"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="E35" s="20" t="s">
+      <c r="E35" s="14" t="s">
         <v>435</v>
       </c>
     </row>
@@ -2751,51 +3136,51 @@
         <v>437</v>
       </c>
     </row>
-    <row r="37" spans="1:5" s="16" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A37" s="14"/>
-      <c r="B37" s="15" t="s">
+    <row r="37" spans="1:5" s="1" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="5"/>
+      <c r="B37" s="6" t="s">
         <v>438</v>
       </c>
-      <c r="C37" s="20" t="s">
+      <c r="C37" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="D37" s="15" t="s">
+      <c r="D37" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="E37" s="20" t="s">
+      <c r="E37" s="14" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="38" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="14"/>
-      <c r="B38" s="15"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="15" t="s">
+    <row r="38" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="5"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="6" t="s">
         <v>441</v>
       </c>
-      <c r="E38" s="20" t="s">
+      <c r="E38" s="14" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="39" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="14"/>
-      <c r="B39" s="15"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="15" t="s">
+    <row r="39" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="5"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="E39" s="20" t="s">
+      <c r="E39" s="14" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="40" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="14"/>
-      <c r="B40" s="15"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="15" t="s">
+    <row r="40" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="5"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="E40" s="20" t="s">
+      <c r="E40" s="14" t="s">
         <v>446</v>
       </c>
     </row>
@@ -2810,51 +3195,51 @@
         <v>448</v>
       </c>
     </row>
-    <row r="42" spans="1:5" s="16" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A42" s="14"/>
-      <c r="B42" s="15" t="s">
+    <row r="42" spans="1:5" s="1" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="5"/>
+      <c r="B42" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="C42" s="20" t="s">
+      <c r="C42" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D42" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="E42" s="20" t="s">
+      <c r="E42" s="14" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="43" spans="1:5" s="16" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="14"/>
-      <c r="B43" s="15"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="15" t="s">
+    <row r="43" spans="1:5" s="1" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="5"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="E43" s="20" t="s">
+      <c r="E43" s="14" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="44" spans="1:5" s="16" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="14"/>
-      <c r="B44" s="15"/>
-      <c r="C44" s="20"/>
-      <c r="D44" s="15" t="s">
+    <row r="44" spans="1:5" s="1" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="5"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="6" t="s">
         <v>454</v>
       </c>
-      <c r="E44" s="20" t="s">
+      <c r="E44" s="14" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="45" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="14"/>
-      <c r="B45" s="15"/>
-      <c r="C45" s="20"/>
-      <c r="D45" s="15" t="s">
+    <row r="45" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="5"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="E45" s="20" t="s">
+      <c r="E45" s="14" t="s">
         <v>457</v>
       </c>
     </row>
@@ -2869,136 +3254,124 @@
         <v>459</v>
       </c>
     </row>
-    <row r="47" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A47" s="14"/>
-      <c r="B47" s="15"/>
-      <c r="C47" s="20"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="20"/>
-    </row>
-    <row r="48" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A48" s="14"/>
-      <c r="B48" s="15"/>
-      <c r="C48" s="20"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="20"/>
-    </row>
-    <row r="49" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A49" s="14"/>
-      <c r="B49" s="15"/>
-      <c r="C49" s="20"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="20"/>
-    </row>
-    <row r="50" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="14"/>
-      <c r="B50" s="15"/>
-      <c r="C50" s="20"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="20"/>
-    </row>
-    <row r="51" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="14"/>
-      <c r="B51" s="15"/>
-      <c r="C51" s="20"/>
-      <c r="D51" s="15"/>
-      <c r="E51" s="20"/>
-    </row>
-    <row r="52" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="14"/>
-      <c r="B52" s="15"/>
-      <c r="C52" s="20"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="20"/>
-    </row>
-    <row r="53" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="14"/>
-      <c r="B53" s="15"/>
-      <c r="C53" s="20"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="20"/>
-    </row>
-    <row r="54" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A54" s="14"/>
-      <c r="B54" s="15"/>
-      <c r="C54" s="20"/>
-      <c r="D54" s="15"/>
-      <c r="E54" s="20"/>
-    </row>
-    <row r="55" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A55" s="14"/>
-      <c r="B55" s="15"/>
-      <c r="C55" s="20"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="20"/>
-    </row>
-    <row r="56" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="14"/>
-      <c r="B56" s="15"/>
-      <c r="C56" s="20"/>
-      <c r="D56" s="15"/>
-      <c r="E56" s="20"/>
-    </row>
-    <row r="57" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="14"/>
-      <c r="B57" s="15"/>
-      <c r="C57" s="20"/>
-      <c r="D57" s="15"/>
-      <c r="E57" s="20"/>
-    </row>
-    <row r="58" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A58" s="14"/>
-      <c r="B58" s="15"/>
-      <c r="C58" s="20"/>
-      <c r="D58" s="15"/>
-      <c r="E58" s="20"/>
-    </row>
-    <row r="59" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A59" s="14"/>
-      <c r="B59" s="15"/>
-      <c r="C59" s="20"/>
-      <c r="D59" s="15"/>
-      <c r="E59" s="20"/>
-    </row>
-    <row r="60" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A60" s="14"/>
-      <c r="B60" s="15"/>
-      <c r="C60" s="20"/>
-      <c r="D60" s="15"/>
-      <c r="E60" s="20"/>
-    </row>
-    <row r="61" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A61" s="14"/>
-      <c r="B61" s="15"/>
-      <c r="C61" s="20"/>
-      <c r="D61" s="15"/>
-      <c r="E61" s="20"/>
-    </row>
-    <row r="62" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A62" s="14"/>
-      <c r="B62" s="15"/>
-      <c r="C62" s="20"/>
-      <c r="D62" s="15"/>
-      <c r="E62" s="20"/>
-    </row>
-    <row r="63" spans="1:5" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A63" s="14"/>
-      <c r="B63" s="15"/>
-      <c r="C63" s="20"/>
-      <c r="D63" s="15"/>
-      <c r="E63" s="20"/>
-    </row>
-    <row r="64" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C64" s="21"/>
-      <c r="E64" s="21"/>
-    </row>
-    <row r="65" spans="3:5" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C65" s="21"/>
-      <c r="E65" s="21"/>
-    </row>
-    <row r="66" spans="3:5" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C66" s="21"/>
-      <c r="E66" s="21"/>
+    <row r="47" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="5"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="14"/>
+    </row>
+    <row r="48" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="5"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="14"/>
+    </row>
+    <row r="49" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="5"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="14"/>
+    </row>
+    <row r="50" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="5"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="14"/>
+    </row>
+    <row r="51" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="5"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="14"/>
+    </row>
+    <row r="52" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="5"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="14"/>
+    </row>
+    <row r="53" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="5"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="14"/>
+    </row>
+    <row r="54" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="5"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="14"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="14"/>
+    </row>
+    <row r="55" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="5"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="14"/>
+    </row>
+    <row r="56" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="5"/>
+      <c r="B56" s="6"/>
+      <c r="C56" s="14"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="14"/>
+    </row>
+    <row r="57" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="5"/>
+      <c r="B57" s="6"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="14"/>
+    </row>
+    <row r="58" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="5"/>
+      <c r="B58" s="6"/>
+      <c r="C58" s="14"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="14"/>
+    </row>
+    <row r="59" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A59" s="5"/>
+      <c r="B59" s="6"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="14"/>
+    </row>
+    <row r="60" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="5"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="14"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="14"/>
+    </row>
+    <row r="61" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A61" s="5"/>
+      <c r="B61" s="6"/>
+      <c r="C61" s="14"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="14"/>
+    </row>
+    <row r="62" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="5"/>
+      <c r="B62" s="6"/>
+      <c r="C62" s="14"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="14"/>
+    </row>
+    <row r="63" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A63" s="5"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="14"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3019,34 +3392,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
     </row>
     <row r="4" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
@@ -4419,6 +4792,534 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4549D9D6-C55A-4567-9D57-9445E24FCAD3}">
+  <dimension ref="A1:E53"/>
+  <sheetFormatPr defaultRowHeight="13.8" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="33.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="104.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="2" customFormat="1" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="1" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>478</v>
+      </c>
+      <c r="C3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>533</v>
+      </c>
+      <c r="C4" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>480</v>
+      </c>
+      <c r="C5" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>482</v>
+      </c>
+      <c r="C6" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>531</v>
+      </c>
+      <c r="C7" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="1" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="7"/>
+      <c r="B8" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>530</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+    </row>
+    <row r="9" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="18" t="s">
+        <v>485</v>
+      </c>
+      <c r="B9" t="s">
+        <v>486</v>
+      </c>
+      <c r="C9" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>489</v>
+      </c>
+      <c r="C11" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>490</v>
+      </c>
+      <c r="C12" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" s="1" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="7"/>
+      <c r="B14" s="8" t="s">
+        <v>535</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+    </row>
+    <row r="15" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="19" t="s">
+        <v>538</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>537</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>539</v>
+      </c>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+    </row>
+    <row r="16" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="19"/>
+      <c r="B16" s="20" t="s">
+        <v>540</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>541</v>
+      </c>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+    </row>
+    <row r="17" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="19"/>
+      <c r="B17" s="20" t="s">
+        <v>542</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>543</v>
+      </c>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+    </row>
+    <row r="18" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="19"/>
+      <c r="B18" s="20" t="s">
+        <v>544</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>545</v>
+      </c>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+    </row>
+    <row r="19" spans="1:5" s="1" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="7"/>
+      <c r="B19" s="8" t="s">
+        <v>546</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+    </row>
+    <row r="20" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="18" t="s">
+        <v>493</v>
+      </c>
+      <c r="B20" t="s">
+        <v>494</v>
+      </c>
+      <c r="C20" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="18"/>
+      <c r="B21" s="21" t="s">
+        <v>548</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>495</v>
+      </c>
+      <c r="C22" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>496</v>
+      </c>
+      <c r="C24" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>498</v>
+      </c>
+      <c r="C25" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>554</v>
+      </c>
+      <c r="C26" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" s="1" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="7"/>
+      <c r="B27" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+    </row>
+    <row r="28" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="19" t="s">
+        <v>556</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>557</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>558</v>
+      </c>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+    </row>
+    <row r="29" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="19"/>
+      <c r="B29" s="20" t="s">
+        <v>559</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>560</v>
+      </c>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+    </row>
+    <row r="30" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="19"/>
+      <c r="B30" s="20" t="s">
+        <v>561</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>562</v>
+      </c>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+    </row>
+    <row r="31" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="19"/>
+      <c r="B31" s="20" t="s">
+        <v>563</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+    </row>
+    <row r="32" spans="1:5" s="1" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="7"/>
+      <c r="B32" s="8" t="s">
+        <v>565</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>566</v>
+      </c>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+    </row>
+    <row r="33" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="18" t="s">
+        <v>501</v>
+      </c>
+      <c r="B33" t="s">
+        <v>502</v>
+      </c>
+      <c r="C33" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>504</v>
+      </c>
+      <c r="C34" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>506</v>
+      </c>
+      <c r="C35" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>508</v>
+      </c>
+      <c r="C36" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" s="1" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="7"/>
+      <c r="B37" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+    </row>
+    <row r="38" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="18" t="s">
+        <v>512</v>
+      </c>
+      <c r="B38" t="s">
+        <v>569</v>
+      </c>
+      <c r="C38" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
+        <v>514</v>
+      </c>
+      <c r="C39" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
+        <v>515</v>
+      </c>
+      <c r="C40" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B41" t="s">
+        <v>517</v>
+      </c>
+      <c r="C41" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" s="1" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="7"/>
+      <c r="B42" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>568</v>
+      </c>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+    </row>
+    <row r="43" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="18" t="s">
+        <v>520</v>
+      </c>
+      <c r="B43" t="s">
+        <v>521</v>
+      </c>
+      <c r="C43" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B44" t="s">
+        <v>523</v>
+      </c>
+      <c r="C44" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B45" t="s">
+        <v>525</v>
+      </c>
+      <c r="C45" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B46" t="s">
+        <v>527</v>
+      </c>
+      <c r="C46" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B47" t="s">
+        <v>529</v>
+      </c>
+      <c r="C47" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" s="1" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="7"/>
+      <c r="B48" s="8" t="s">
+        <v>571</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>572</v>
+      </c>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+    </row>
+    <row r="49" spans="1:3" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="B49" t="s">
+        <v>576</v>
+      </c>
+      <c r="C49" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B50" t="s">
+        <v>578</v>
+      </c>
+      <c r="C50" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B51" t="s">
+        <v>580</v>
+      </c>
+      <c r="C51" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B52" t="s">
+        <v>582</v>
+      </c>
+      <c r="C52" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B53" t="s">
+        <v>584</v>
+      </c>
+      <c r="C53" t="s">
+        <v>585</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55841D51-0A9A-488F-AC9D-07EF912AF8EC}">
   <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="13.95" customHeight="1" x14ac:dyDescent="0.3"/>
